--- a/evaluation/analysis_of_results/analyzed/analyzed_results_step_3.xlsx
+++ b/evaluation/analysis_of_results/analyzed/analyzed_results_step_3.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per Scenario Execution" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregated Per Execution" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregated Per Scenario" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per Scenario by Field" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1195,4 +1196,554 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>TP_sum</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FP_sum</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FN_sum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>precision_mean</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>precision_std</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>precision_count</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>recall_mean</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>recall_std</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>f1_mean</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>f1_std</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>precision_cv</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>recall_cv</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>f1_cv</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SIM_card_scenario</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>deviation_type</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SIM_card_scenario</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>reasoning_about_root_cause</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1775179006241816</v>
+      </c>
+      <c r="H3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.9523809523809524</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1183452670827877</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1911731237491187</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.1242625304369271</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SIM_card_scenario</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>reference_in_model</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>blood_donation_scenario</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>deviation_type</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3511066249289032</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3511066249289032</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3511066249289032</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4130666175634156</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4130666175634156</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4130666175634156</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>blood_donation_scenario</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>reasoning_about_root_cause</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.319841914974746</v>
+      </c>
+      <c r="H6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.319841914974746</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.319841914974746</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.3690483634323992</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3690483634323992</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3690483634323992</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>blood_donation_scenario</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>reference_in_model</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>33</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.319841914974746</v>
+      </c>
+      <c r="H7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.319841914974746</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.319841914974746</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3690483634323992</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3690483634323992</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3690483634323992</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>emergencies_scenario</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>deviation_type</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2355041079768029</v>
+      </c>
+      <c r="H8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2355041079768029</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2355041079768029</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2497770842178212</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2497770842178212</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2497770842178212</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>emergencies_scenario</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>reasoning_about_root_cause</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>42</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2662768509362723</v>
+      </c>
+      <c r="H9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2355041079768027</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.9102040816326531</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2468344142012429</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.298230073048625</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2497770842178211</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2711857913870158</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>emergencies_scenario</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>reference_in_model</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>47</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1690308509457033</v>
+      </c>
+      <c r="H10" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1690308509457033</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.1690308509457033</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1740023465617534</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1740023465617534</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1740023465617534</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>